--- a/InputData/trans/BLP/BAU LCFS Perc.xlsx
+++ b/InputData/trans/BLP/BAU LCFS Perc.xlsx
@@ -1,34 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27210"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roman.hennig\World Resources Institute\TRAC City - HK 2050 is now\InputData FOR HONG KONG\UPDATE InputData for Hong Kong\InputData\trans\BLP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganM\Documents\eps-us\InputData\trans\BLP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_309C0F6B18950C1306216083BC9DD15C2F6F9EB4" xr6:coauthVersionLast="36" xr6:coauthVersionMax="43" xr10:uidLastSave="{7E601781-8EAB-4747-A73D-63848E94F8AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B1475BDE77FEBFEB6E86A18DC81CFA2EA4E44D72" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="21075" windowHeight="13110" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BLP" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>BLP BAU LCFS Percentage</t>
   </si>
@@ -36,16 +34,31 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>None</t>
+    <t>None needed</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>BAU LCFS Perc</t>
+    <t>The National Renewable Fuel Standard is specified in gallons of renewable fuel</t>
   </si>
   <si>
-    <t>NoLow Carbon Fuel Standard is specified for Hong Kong.</t>
+    <t>and a requirement for percent decarbonization of that fuel relative to a baseline</t>
+  </si>
+  <si>
+    <t>fuel type.  We convert from gallons to a share of total fuel, then multiply by the</t>
+  </si>
+  <si>
+    <t>required decarbonization percentage, to convert the policy into the form</t>
+  </si>
+  <si>
+    <t>needed for the LCFS in the EPS.</t>
+  </si>
+  <si>
+    <t>No BAU LCFS is specified for the US.</t>
+  </si>
+  <si>
+    <t>BAU LCFS Perc (dimensionless)</t>
   </si>
 </sst>
 </file>
@@ -55,7 +68,14 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,16 +111,301 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -144,41 +449,264 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="8">
-    <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Font: Calibri, 9pt regular" xfId="6" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Footnotes: top row" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Header: bottom row" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+  <cellStyles count="63">
+    <cellStyle name="20% - Accent1" xfId="25" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent2" xfId="28" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent3" xfId="31" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Accent4" xfId="34" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Accent5" xfId="37" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Accent6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="40% - Accent1" xfId="26" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1 2" xfId="51" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="40% - Accent2" xfId="29" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="40% - Accent3" xfId="32" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="40% - Accent4" xfId="35" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="40% - Accent5" xfId="38" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5 2" xfId="59" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="40% - Accent6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="43" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Accent1" xfId="24" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="27" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="30" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="33" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="36" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="14" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Body: normal cell 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Calculation" xfId="17" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="22" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Font: Calibri, 9pt regular" xfId="6" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Footnotes: top row" xfId="2" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Good" xfId="13" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Header: bottom row" xfId="5" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Heading 1" xfId="9" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="10" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="11" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="15" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="18" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Parent row" xfId="3" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Table title" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Note" xfId="21" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Note 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Output" xfId="16" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Parent row" xfId="3" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="Table title" xfId="7" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="Title" xfId="8" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="23" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="20" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -194,9 +722,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -234,9 +762,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -269,26 +797,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -321,26 +832,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -514,18 +1008,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="56.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -533,14 +1027,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -550,232 +1069,212 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36">
       <c r="B1">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C1">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="D1">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="E1">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="F1">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="G1">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="H1">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="I1">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="J1">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="K1">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="L1">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="M1">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="N1">
-        <v>2028</v>
+        <v>2032</v>
       </c>
       <c r="O1">
-        <v>2029</v>
+        <v>2033</v>
       </c>
       <c r="P1">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="Q1">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="R1">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="S1">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="T1">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="U1">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="V1">
-        <v>2036</v>
+        <v>2040</v>
       </c>
       <c r="W1">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="X1">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="Y1">
-        <v>2039</v>
+        <v>2043</v>
       </c>
       <c r="Z1">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="AA1">
-        <v>2041</v>
+        <v>2045</v>
       </c>
       <c r="AB1">
-        <v>2042</v>
+        <v>2046</v>
       </c>
       <c r="AC1">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="AD1">
-        <v>2044</v>
+        <v>2048</v>
       </c>
       <c r="AE1">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="AF1">
-        <v>2046</v>
-      </c>
-      <c r="AG1">
-        <v>2047</v>
-      </c>
-      <c r="AH1">
-        <v>2048</v>
-      </c>
-      <c r="AI1">
-        <v>2049</v>
-      </c>
-      <c r="AJ1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2">
-        <v>0</v>
-      </c>
-      <c r="U2" s="2">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>0</v>
-      </c>
+    <row r="2" spans="1:36" ht="28.5">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -783,49 +1282,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -833,24 +1315,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -869,70 +1412,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1034,32 +1530,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F3BCE05-1ABB-40C0-A262-96A7D050CAB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B57F3E-CE96-4C85-AF3F-9B8297C6D318}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02ED4C34-246B-4911-91CF-C2EEA96299FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4BE71F-6FC8-421A-BAB1-648A0C5D6C68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E945FA8-1561-4E4B-BB1B-DF48CD44C9B6}"/>
 </file>